--- a/artfynd/A 6906-2026 artfynd.xlsx
+++ b/artfynd/A 6906-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -893,6 +893,108 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133646480</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93206</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>787658</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7249114</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gamla</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6906-2026 artfynd.xlsx
+++ b/artfynd/A 6906-2026 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>133646480</v>
       </c>
       <c r="B4" t="n">
-        <v>93206</v>
+        <v>93208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6906-2026 artfynd.xlsx
+++ b/artfynd/A 6906-2026 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>133646480</v>
       </c>
       <c r="B4" t="n">
-        <v>93208</v>
+        <v>93216</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6906-2026 artfynd.xlsx
+++ b/artfynd/A 6906-2026 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>133646480</v>
       </c>
       <c r="B4" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 6906-2026 artfynd.xlsx
+++ b/artfynd/A 6906-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133251665</v>
+        <v>133646478</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>93271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bräntberget, Bräntberget, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>787727</v>
+        <v>787818</v>
       </c>
       <c r="R2" t="n">
-        <v>7248933</v>
+        <v>7248995</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I grov, död tall.</t>
+          <t>Gamla</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133419160</v>
+        <v>133646480</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>93271</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,49 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>787443</v>
+        <v>787658</v>
       </c>
       <c r="R3" t="n">
-        <v>7248898</v>
+        <v>7249114</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,12 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gamla</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133646480</v>
+        <v>133251665</v>
       </c>
       <c r="B4" t="n">
-        <v>93264</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +890,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Bräntberget, Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>787658</v>
+        <v>787727</v>
       </c>
       <c r="R4" t="n">
-        <v>7249114</v>
+        <v>7248933</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,17 +953,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Gamla</t>
+          <t>I grov, död tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,15 +978,124 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133419160</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bräntberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>787443</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7248898</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6906-2026 artfynd.xlsx
+++ b/artfynd/A 6906-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646480</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133419160</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646478</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133251665</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>